--- a/05_synthesis/comparative_coverage_matrix.xlsx
+++ b/05_synthesis/comparative_coverage_matrix.xlsx
@@ -1,13 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Coverage Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage_v1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Published_TableIII" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codes_v1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,21 +29,14 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -56,10 +51,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -426,15 +424,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="29.7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="41.4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,75 +447,1661 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>cross_provider_iam</t>
+          <t>label</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>policy_enforcement</t>
+          <t>phase</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>audit_traceability</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>governance_gap</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>coverage_notes</t>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_ids</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>STU-0001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - X marks that the study addresses this coded theme</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>EV-014, EV-028, EV-042, EV-056, EV-070, EV-084</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>STU-0002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>EXAMPLE row - X marks that the study addresses this coded theme</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>EV-008, EV-022, EV-036, EV-050, EV-064, EV-078</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>EV-007, EV-021, EV-035, EV-049, EV-063, EV-077</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>EV-003, EV-017, EV-031, EV-045, EV-059, EV-073</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>EV-006, EV-020, EV-034, EV-048, EV-062, EV-076</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>EV-010, EV-024, EV-038, EV-052, EV-066, EV-080</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>EV-004, EV-018, EV-032, EV-046, EV-060, EV-074</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>EV-002, EV-016, EV-030, EV-044, EV-058, EV-072</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>EV-001, EV-015, EV-029, EV-043, EV-057, EV-071</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>EV-013, EV-027, EV-041, EV-055, EV-069, EV-083</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>EV-009, EV-023, EV-037, EV-051, EV-065, EV-079</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>EV-011, EV-025, EV-039, EV-053, EV-067, EV-081</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>EV-005, EV-019, EV-033, EV-047, EV-061, EV-075</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>EV-012, EV-026, EV-040, EV-054, EV-068, EV-082</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="29.7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="34.2" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>identical to v1 workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>identical to v1 workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>identical to v1 workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>differs from v1 workbook on D1, D4, D5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="29.7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>STU-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Yeboah-Ofori et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>D1.4</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>D5.X</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>STU-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Hegde et al. (2023)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>STU-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Diningrat et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>STU-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Aljarrah et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>STU-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Cuzzocrea &amp; Belmerabet (2024)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>STU-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Kaur et al. (2024)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>D1.4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>D5.ID</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>STU-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Alouffi et al. (2021)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>STU-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ali et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>D4.4</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>STU-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>AlGhamdi et al. (2020)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>D5.X</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>STU-10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pöhn &amp; Hillmann (2021)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>D2.X</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>NRM-01</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ISO/IEC 27001:2022</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>NRM-02</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>NIST CSF 2.0 (2024)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>NRM-03</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CSA Security Guidance v5 (2024)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>D1.3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>D2.FW</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>D3.4</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>D4.3</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>D6.IF</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>NRM-04</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NIST SP 800-210 (Hu et al., 2020)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>D1.1</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>D2.PO</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>D3.1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>D5.DE</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>D6.AA</t>
         </is>
       </c>
     </row>
